--- a/Data/fact_medical_crm.xlsx
+++ b/Data/fact_medical_crm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\3\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\3- Andalusia\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8741BA-B0F2-47C1-8640-DCC0721C8B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677B7028-1404-421B-ADDD-991650EE5A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -39,57 +39,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
-  <si>
-    <t>BU Key</t>
-  </si>
-  <si>
-    <t>Date Key</t>
-  </si>
-  <si>
-    <t>Baseline Revenue</t>
-  </si>
-  <si>
-    <t>Actual Revenue</t>
-  </si>
-  <si>
-    <t>Actual Volume</t>
-  </si>
-  <si>
-    <t>Baseline Volume</t>
-  </si>
-  <si>
-    <t>Actual CPV</t>
-  </si>
-  <si>
-    <t>Baseline CPV</t>
-  </si>
-  <si>
-    <t>Target Revenue</t>
-  </si>
-  <si>
-    <t>Target Volume</t>
-  </si>
-  <si>
-    <t>Target CPV</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>20250301</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>20250401</t>
-  </si>
-  <si>
-    <t>20250501</t>
-  </si>
-  <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>baseline_revenue</t>
+  </si>
+  <si>
+    <t>actual_revenue</t>
+  </si>
+  <si>
+    <t>actual_volume</t>
+  </si>
+  <si>
+    <t>baseline_volume</t>
+  </si>
+  <si>
+    <t>actual_cpv</t>
+  </si>
+  <si>
+    <t>baseline_cpv</t>
+  </si>
+  <si>
+    <t>target_revenue</t>
+  </si>
+  <si>
+    <t>target_volume</t>
+  </si>
+  <si>
+    <t>target_cpv</t>
+  </si>
+  <si>
+    <t>bu_key</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -131,10 +122,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,352 +466,352 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>13194275.52</v>
+      </c>
+      <c r="B2" s="1">
+        <v>15131175.839999801</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5393</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5069</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2805.7066271091799</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2602.9346064312499</v>
+      </c>
+      <c r="G2" s="1">
+        <v>15131175.839999801</v>
+      </c>
+      <c r="H2" s="2">
+        <v>5393</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2805.7066271091799</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K2" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>12997447.949999999</v>
+      </c>
+      <c r="B3" s="1">
+        <v>15957777.300000001</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5964</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4937</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2675.6836519114599</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2632.6611201134301</v>
+      </c>
+      <c r="G3" s="1">
+        <v>15957777.300000001</v>
+      </c>
+      <c r="H3" s="2">
+        <v>5964</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2675.6836519114599</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>13194275.52</v>
+      </c>
+      <c r="B4" s="1">
+        <v>4279106.1900000004</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1278</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5069</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3348.28340375587</v>
+      </c>
+      <c r="F4" s="1">
+        <v>2602.9346064312499</v>
+      </c>
+      <c r="G4" s="1">
+        <v>13194275.52</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5069</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2602.9346064312499</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>11108265.07</v>
+      </c>
+      <c r="B5" s="1">
+        <v>7339618.4699999997</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3374</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4873</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2175.34631594546</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2279.5536774061202</v>
+      </c>
+      <c r="G5" s="1">
+        <v>11108265.07</v>
+      </c>
+      <c r="H5" s="2">
+        <v>4873</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2279.5536774061202</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K5" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>10796540.550000001</v>
+      </c>
+      <c r="B6" s="1">
+        <v>12439429.5200001</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4003</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4771</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3107.5267349487999</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2262.95127855795</v>
+      </c>
+      <c r="G6" s="1">
+        <v>12439429.5200001</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4771</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2607.3002557116001</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>11108265.07</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2182256.7400000002</v>
+      </c>
+      <c r="C7" s="2">
+        <v>763</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4873</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2860.10057667104</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2279.5536774061202</v>
+      </c>
+      <c r="G7" s="1">
+        <v>11108265.07</v>
+      </c>
+      <c r="H7" s="2">
+        <v>4873</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2279.5536774061202</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7328549.0899999999</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6116284.8100000303</v>
+      </c>
+      <c r="C8" s="2">
+        <v>7473</v>
+      </c>
+      <c r="D8" s="2">
+        <v>8813</v>
+      </c>
+      <c r="E8" s="1">
+        <v>818.45106516794101</v>
+      </c>
+      <c r="F8" s="1">
+        <v>831.56122659707296</v>
+      </c>
+      <c r="G8" s="1">
+        <v>7328549.0899999999</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8813</v>
+      </c>
+      <c r="I8" s="1">
+        <v>831.56122659707296</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1">
-        <v>13194275.52</v>
-      </c>
-      <c r="D2" s="1">
-        <v>15131175.839999801</v>
-      </c>
-      <c r="E2" s="2">
-        <v>5393</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5069</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2805.7066271091799</v>
-      </c>
-      <c r="H2" s="1">
-        <v>2602.9346064312499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>15131175.839999801</v>
-      </c>
-      <c r="J2" s="2">
-        <v>5393</v>
-      </c>
-      <c r="K2" s="1">
-        <v>2805.7066271091799</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1">
-        <v>11108265.07</v>
-      </c>
-      <c r="D3" s="1">
-        <v>7339618.4699999997</v>
-      </c>
-      <c r="E3" s="2">
-        <v>3374</v>
-      </c>
-      <c r="F3" s="2">
-        <v>4873</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2175.34631594546</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2279.5536774061202</v>
-      </c>
-      <c r="I3" s="1">
-        <v>11108265.07</v>
-      </c>
-      <c r="J3" s="2">
-        <v>4873</v>
-      </c>
-      <c r="K3" s="1">
-        <v>2279.5536774061202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1">
-        <v>12997447.949999999</v>
-      </c>
-      <c r="D4" s="1">
-        <v>15957777.300000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>5964</v>
-      </c>
-      <c r="F4" s="2">
-        <v>4937</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2675.6836519114599</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2632.6611201134301</v>
-      </c>
-      <c r="I4" s="1">
-        <v>15957777.300000001</v>
-      </c>
-      <c r="J4" s="2">
-        <v>5964</v>
-      </c>
-      <c r="K4" s="1">
-        <v>2675.6836519114599</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>13194275.52</v>
-      </c>
-      <c r="D5" s="1">
-        <v>4279106.1900000004</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1278</v>
-      </c>
-      <c r="F5" s="2">
-        <v>5069</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3348.28340375587</v>
-      </c>
-      <c r="H5" s="1">
-        <v>2602.9346064312499</v>
-      </c>
-      <c r="I5" s="1">
-        <v>13194275.52</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5069</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2602.9346064312499</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10796540.550000001</v>
-      </c>
-      <c r="D6" s="1">
-        <v>12439429.5200001</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4003</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4771</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3107.5267349487999</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2262.95127855795</v>
-      </c>
-      <c r="I6" s="1">
-        <v>12439429.5200001</v>
-      </c>
-      <c r="J6" s="2">
-        <v>4771</v>
-      </c>
-      <c r="K6" s="1">
-        <v>2607.3002557116001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1">
-        <v>11108265.07</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2182256.7400000002</v>
-      </c>
-      <c r="E7" s="2">
-        <v>763</v>
-      </c>
-      <c r="F7" s="2">
-        <v>4873</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2860.10057667104</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2279.5536774061202</v>
-      </c>
-      <c r="I7" s="1">
-        <v>11108265.07</v>
-      </c>
-      <c r="J7" s="2">
-        <v>4873</v>
-      </c>
-      <c r="K7" s="1">
-        <v>2279.5536774061202</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="K8" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7100650.9199999999</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8387898.9400000703</v>
+      </c>
+      <c r="C9" s="2">
+        <v>9066</v>
+      </c>
+      <c r="D9" s="2">
+        <v>8517</v>
+      </c>
+      <c r="E9" s="1">
+        <v>925.20394220163996</v>
+      </c>
+      <c r="F9" s="1">
+        <v>833.70328989080701</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8387898.9400000703</v>
+      </c>
+      <c r="H9" s="2">
+        <v>9066</v>
+      </c>
+      <c r="I9" s="1">
+        <v>925.20394220163996</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>7328549.0899999999</v>
       </c>
-      <c r="D8" s="1">
-        <v>6116284.8100000303</v>
-      </c>
-      <c r="E8" s="2">
-        <v>7473</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="B10" s="1">
+        <v>3117051.97</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2290</v>
+      </c>
+      <c r="D10" s="2">
         <v>8813</v>
       </c>
-      <c r="G8" s="1">
-        <v>818.45106516794101</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="E10" s="1">
+        <v>1361.1580655021801</v>
+      </c>
+      <c r="F10" s="1">
         <v>831.56122659707296</v>
       </c>
-      <c r="I8" s="1">
+      <c r="G10" s="1">
         <v>7328549.0899999999</v>
       </c>
-      <c r="J8" s="2">
+      <c r="H10" s="2">
         <v>8813</v>
       </c>
-      <c r="K8" s="1">
+      <c r="I10" s="1">
         <v>831.56122659707296</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1">
-        <v>7100650.9199999999</v>
-      </c>
-      <c r="D9" s="1">
-        <v>8387898.9400000703</v>
-      </c>
-      <c r="E9" s="2">
-        <v>9066</v>
-      </c>
-      <c r="F9" s="2">
-        <v>8517</v>
-      </c>
-      <c r="G9" s="1">
-        <v>925.20394220163996</v>
-      </c>
-      <c r="H9" s="1">
-        <v>833.70328989080701</v>
-      </c>
-      <c r="I9" s="1">
-        <v>8387898.9400000703</v>
-      </c>
-      <c r="J9" s="2">
-        <v>9066</v>
-      </c>
-      <c r="K9" s="1">
-        <v>925.20394220163996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7328549.0899999999</v>
-      </c>
-      <c r="D10" s="1">
-        <v>3117051.97</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2290</v>
-      </c>
-      <c r="F10" s="2">
-        <v>8813</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1361.1580655021801</v>
-      </c>
-      <c r="H10" s="1">
-        <v>831.56122659707296</v>
-      </c>
-      <c r="I10" s="1">
-        <v>7328549.0899999999</v>
-      </c>
-      <c r="J10" s="2">
-        <v>8813</v>
-      </c>
-      <c r="K10" s="1">
-        <v>831.56122659707296</v>
+      <c r="J10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>45778</v>
       </c>
     </row>
   </sheetData>
